--- a/output/pdf_financials_xlsx/SCOT.xlsx
+++ b/output/pdf_financials_xlsx/SCOT.xlsx
@@ -6601,7 +6601,7 @@
         <v>0.11303</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>-0.44481</v>
+        <v>-0.44881</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>-0.002923</v>
@@ -6613,13 +6613,13 @@
         <v>-0.312981</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.079263</v>
+        <v>-0.749736</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.609123</v>
+        <v>0.347639</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.980953</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0</v>
@@ -24294,7 +24294,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SCOT.xlsx
+++ b/output/pdf_financials_xlsx/SCOT.xlsx
@@ -999,19 +999,19 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>5.3e-05</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.024857</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.212679</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.263261</v>
       </c>
     </row>
     <row r="13">
@@ -1851,19 +1851,19 @@
         <v>-3.870144</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-6.391312</v>
+        <v>-6.391365</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-9.515791</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-19.074047</v>
+        <v>-19.098904</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.89035</v>
+        <v>-4.103029</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-10.939074</v>
+        <v>-11.202335</v>
       </c>
     </row>
     <row r="28">
@@ -1955,19 +1955,19 @@
         <v>-3.870144</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-6.391312</v>
+        <v>-6.391365</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-9.515791</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-19.074047</v>
+        <v>-19.098904</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.89035</v>
+        <v>-4.103029</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-10.939074</v>
+        <v>-11.202335</v>
       </c>
     </row>
     <row r="30">
@@ -2200,31 +2200,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.211185</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.092352</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.003416</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.001345</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000905</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.053581</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.339819</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.477576</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.18204</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>4.742872</v>
@@ -2242,7 +2242,7 @@
         <v>9.299574</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>13.152786</v>
       </c>
     </row>
     <row r="35">
@@ -2304,31 +2304,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.211185</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.092352</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.003416</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.001345</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000905</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.053581</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.339819</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.477576</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.18204</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>4.742872</v>
@@ -2346,7 +2346,7 @@
         <v>9.299574</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>13.152786</v>
       </c>
     </row>
     <row r="37">
@@ -2928,31 +2928,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.211717</v>
+        <v>0.000532</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.094627</v>
+        <v>0.002275</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.012946</v>
+        <v>0.00953</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.005435</v>
+        <v>0.00409</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.004095</v>
+        <v>0.00319</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.07302599999999999</v>
+        <v>0.019445</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.46735</v>
+        <v>0.127531</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.57526</v>
+        <v>0.09768400000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.300615</v>
+        <v>0.118575</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>1.630141</v>
@@ -2970,7 +2970,7 @@
         <v>0.20495</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>13.271983</v>
+        <v>0.119197</v>
       </c>
     </row>
     <row r="49">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -8120,7 +8120,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -9405,7 +9409,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -28920,7 +28928,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -31373,7 +31381,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">

--- a/output/pdf_financials_xlsx/SCOT.xlsx
+++ b/output/pdf_financials_xlsx/SCOT.xlsx
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.011001</v>
+        <v>0.043001</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.08323700000000001</v>
@@ -718,22 +718,22 @@
         <v>0.096161</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.027179</v>
+        <v>0.075179</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.034376</v>
+        <v>0.082376</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.07799499999999999</v>
+        <v>0.125995</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.071515</v>
+        <v>0.146515</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.035487</v>
+        <v>0.191487</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.12451</v>
+        <v>0.29851</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.7044550000000001</v>
@@ -831,7 +831,7 @@
         <v>0.008920000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.010087</v>
+        <v>0.070087</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>0.272058</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.011001</v>
+        <v>0.043001</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.08323700000000001</v>
@@ -880,16 +880,16 @@
         <v>4e-06</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.08691500000000001</v>
+        <v>0.134915</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.08160199999999999</v>
+        <v>0.216602</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.307545</v>
+        <v>0.463545</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.201314</v>
+        <v>0.375314</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>4.118885</v>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>0</v>
+        <v>0.244054</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>0.163366</v>
@@ -3493,16 +3493,16 @@
         <v>0.588426</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0</v>
+        <v>0.901407</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0</v>
+        <v>1.628249</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0</v>
+        <v>1.335029</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0</v>
+        <v>2.323891</v>
       </c>
       <c r="K58" s="3" t="n">
         <v>0.018562</v>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>0.248054</v>
+        <v>0.004</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>0.004</v>
@@ -3649,16 +3649,16 @@
         <v>0.00419</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.006153</v>
+        <v>0.104746</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>1.706495</v>
+        <v>0.078246</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>1.404275</v>
+        <v>0.069246</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>2.430891</v>
+        <v>0.107</v>
       </c>
       <c r="K61" s="3" t="n">
         <v>2.433749</v>
@@ -3909,16 +3909,16 @@
         <v>0</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0</v>
+        <v>0.0282</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0</v>
+        <v>0.153002</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0</v>
+        <v>0.117506</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0</v>
+        <v>0.22274</v>
       </c>
       <c r="K66" s="3" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0</v>
+        <v>0.242457</v>
       </c>
       <c r="K69" s="3" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.242457</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>0.117506</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.465197</v>
+        <v>0.22274</v>
       </c>
       <c r="K75" s="3" t="n">
         <v>0</v>
@@ -4667,10 +4667,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J80" s="3" t="n">
+        <v>0.1270900187549993</v>
       </c>
       <c r="K80" s="1" t="inlineStr">
         <is>
@@ -5080,7 +5078,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>0.559209</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>1.2996</v>
@@ -5092,19 +5090,19 @@
         <v>1.649601</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>1.914701</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>2.463528</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>3.874048</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>4.662451</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>5.423549</v>
       </c>
       <c r="K88" s="3" t="n">
         <v>16.311711</v>
@@ -5288,7 +5286,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.3585</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0.3585</v>
@@ -12653,7 +12651,11 @@
           <t>Exploration and evaluation assets – Note 5 and 6</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -12910,7 +12912,11 @@
           <t>Loans payable – Notes 6 and 7</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -13001,7 +13007,11 @@
           <t>Due to related parties – Note 6</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -13082,7 +13092,11 @@
           <t>Share capital – Note 8</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -13610,7 +13624,11 @@
           <t>Exploration and evaluation assets – Notes 5 and 6</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
         <v>0.244054</v>
       </c>
@@ -13693,7 +13711,11 @@
           <t>Share capital – Note 7</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -14763,7 +14785,11 @@
           <t>Share capital – Note 7</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
         <v>0.559209</v>
       </c>
@@ -16029,7 +16055,11 @@
           <t>Contributed surplus – Note 9</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E96" s="5" t="n">
         <v>0.3585</v>
       </c>
@@ -33492,7 +33522,11 @@
           <t>Management fees – Note 6</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -34655,7 +34689,11 @@
           <t>Consulting – Note 6</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -35719,7 +35757,11 @@
           <t>Management fees – Note 6</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E316" s="5" t="n">
         <v>0.032</v>
       </c>

--- a/output/pdf_financials_xlsx/SCOT.xlsx
+++ b/output/pdf_financials_xlsx/SCOT.xlsx
@@ -3973,22 +3973,22 @@
         <v>0</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.02392</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.058378</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.491052</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.329966</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.351486</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.7906879999999999</v>
       </c>
     </row>
     <row r="68">
@@ -5709,31 +5709,31 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.010068</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.009325999999999999</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00578</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.005757</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000237</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.01671</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.008333</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.007258</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000336</v>
       </c>
       <c r="K101" s="3" t="n">
         <v>-0.159116</v>
@@ -5969,31 +5969,31 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.042585</v>
+        <v>0.032517</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.09032900000000001</v>
+        <v>-0.08100300000000001</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.012143</v>
+        <v>-0.017923</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.06804300000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.069243</v>
+        <v>0.069006</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.086058</v>
+        <v>0.06934800000000001</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.003026</v>
+        <v>0.011359</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.188124</v>
+        <v>0.180866</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.037786</v>
+        <v>0.03745</v>
       </c>
       <c r="K106" s="3" t="n">
         <v>-0.313315</v>
@@ -23743,7 +23743,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -24680,7 +24684,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -25194,7 +25202,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -25273,7 +25285,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E200" s="5" t="n">
         <v>0.508</v>
       </c>
@@ -27993,7 +28009,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E230" s="5" t="n">
         <v>-0.010068</v>
       </c>
